--- a/data/thesis_outputs/tables/TABLE_3-1.xlsx
+++ b/data/thesis_outputs/tables/TABLE_3-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALCULATION" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PAPER_TABLE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALCULATION" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TABLE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>원본 Stage0 manifest의 파일별 rows_raw를 재무제표 유형별로 합산하고, 다섯 유형의 합계가 동일한지 확인. 추가 표본 필터는 적용하지 않음.</t>
+          <t>원본 Stage0 기록의 파일별 rows_raw를 재무제표 유형별로 합산하고 다섯 유형의 합계를 확인. 표본 범위는 원본 Stage0 producer 입력과 동일.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>원본 Stage0 producer가 실제로 읽은 다섯 재무제표 유형은 각각 75,721개 행입니다. 원본 producer에는 별도의 기업 단위 금융업 제외가 구현되어 있지 않으므로, 이 Excel 생성 과정도 임의의 금융업 제외를 추가하지 않습니다.</t>
+          <t>원본 Stage0 producer가 실제로 읽은 다섯 재무제표 유형은 각각 75,721개 행입니다. 원본 producer는 기업 단위 금융업 제외 전의 표본을 사용하며, 이 Excel도 같은 표본 구성을 따릅니다.</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>원본 Stage1 metadata의 firm_year_rows를 읽음. Excel 생성 단계에서 별도 산업 필터를 적용하지 않음.</t>
+          <t>원본 Stage1 metadata의 firm_year_rows를 읽음. 표본 범위는 Stage1 producer의 결합 결과와 동일.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>이 FrozenReplay의 과거 Stage1 산출물에는 금융업 제외 내역이 남아 있지 않습니다. 4,924라는 숫자는 다시 읽을 수 있지만 비금융 표본이라는 의미까지 확인한 것으로 보지 않습니다.</t>
+          <t>이 FrozenReplay의 과거 Stage1 산출물은 금융업 분류 항목이 미기록 상태입니다. 4,924는 등급 결합 표본으로 표기합니다.</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Oracle 모형을 개발하는 기업-연도. OOT 기간은 포함하지 않음.</t>
+          <t>Oracle 모형 개발에 사용한 2002–2019년 기업-연도.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
